--- a/Results_experiment/exp_5/summary.xlsx
+++ b/Results_experiment/exp_5/summary.xlsx
@@ -447,13 +447,13 @@
         <v>3055</v>
       </c>
       <c r="D2">
-        <v>0.6979521413387169</v>
+        <v>0.6986106156096008</v>
       </c>
       <c r="E2">
-        <v>3.250103087257191</v>
+        <v>3.246558488529645</v>
       </c>
       <c r="F2">
-        <v>2.159982861758937</v>
+        <v>2.121843074047526</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -467,13 +467,13 @@
         <v>3014</v>
       </c>
       <c r="D3">
-        <v>0.5174000462435804</v>
+        <v>0.5197746414101002</v>
       </c>
       <c r="E3">
-        <v>5.418578061391223</v>
+        <v>5.405230778707071</v>
       </c>
       <c r="F3">
-        <v>3.741917197618813</v>
+        <v>3.728763095021347</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -487,13 +487,13 @@
         <v>2753</v>
       </c>
       <c r="D4">
-        <v>0.581817122932818</v>
+        <v>0.5949211825165797</v>
       </c>
       <c r="E4">
-        <v>4.545674830341616</v>
+        <v>4.473886987236828</v>
       </c>
       <c r="F4">
-        <v>3.156861759816886</v>
+        <v>3.160887711953554</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -507,13 +507,13 @@
         <v>2231</v>
       </c>
       <c r="D5">
-        <v>0.3541639863149695</v>
+        <v>0.378576053670066</v>
       </c>
       <c r="E5">
-        <v>2.572267396313577</v>
+        <v>2.523184312977908</v>
       </c>
       <c r="F5">
-        <v>1.638315985650157</v>
+        <v>1.609705173845926</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -527,13 +527,13 @@
         <v>1838</v>
       </c>
       <c r="D6">
-        <v>0.3969942829403442</v>
+        <v>0.3945181764904004</v>
       </c>
       <c r="E6">
-        <v>3.632702585412588</v>
+        <v>3.640153379839862</v>
       </c>
       <c r="F6">
-        <v>2.488376125835044</v>
+        <v>2.520609159002324</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -547,13 +547,13 @@
         <v>1534</v>
       </c>
       <c r="D7">
-        <v>0.6899041310981555</v>
+        <v>0.7203748747431948</v>
       </c>
       <c r="E7">
-        <v>3.312712742220745</v>
+        <v>3.145747670914981</v>
       </c>
       <c r="F7">
-        <v>2.35434339794934</v>
+        <v>2.206674914940561</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -567,13 +567,13 @@
         <v>1348</v>
       </c>
       <c r="D8">
-        <v>0.3653210770710931</v>
+        <v>0.4556710193033372</v>
       </c>
       <c r="E8">
-        <v>2.677870893787064</v>
+        <v>2.479952287925068</v>
       </c>
       <c r="F8">
-        <v>1.921681346275188</v>
+        <v>1.82753116135244</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -587,13 +587,13 @@
         <v>572</v>
       </c>
       <c r="D9">
-        <v>0.01980771632039202</v>
+        <v>0.07963627431086817</v>
       </c>
       <c r="E9">
-        <v>6.514470733283882</v>
+        <v>6.312526937594884</v>
       </c>
       <c r="F9">
-        <v>4.267102143945901</v>
+        <v>3.940551865489586</v>
       </c>
     </row>
   </sheetData>
